--- a/references/01 - Tai lieu du an/1. Ke hoach phat hieu yeu cau BTL (Elicitation)/Product_Backlog_Sprint_Plan.xlsx
+++ b/references/01 - Tai lieu du an/1. Ke hoach phat hieu yeu cau BTL (Elicitation)/Product_Backlog_Sprint_Plan.xlsx
@@ -2045,7 +2045,7 @@
     <t>Todo</t>
   </si>
   <si>
-    <t>Xuyên suốt. Cần nhóm thống nhất SQ-03 trước. Kế hoạch này không tạo GitHub Project.</t>
+    <t>Xuyên suốt. Cần nhóm thống nhất SQ-03 trước.</t>
   </si>
   <si>
     <t>S1-T02</t>

--- a/references/01 - Tai lieu du an/1. Ke hoach phat hieu yeu cau BTL (Elicitation)/Product_Backlog_Sprint_Plan.xlsx
+++ b/references/01 - Tai lieu du an/1. Ke hoach phat hieu yeu cau BTL (Elicitation)/Product_Backlog_Sprint_Plan.xlsx
@@ -1049,7 +1049,7 @@
     <t>Unplanned (ở lại Product Backlog)</t>
   </si>
   <si>
-    <t>Won't (stories)</t>
+    <t>Không sử dụng (story)</t>
   </si>
   <si>
     <t>Roadmap (v2.0, không có story)</t>
@@ -1058,7 +1058,7 @@
     <t>Total Story Points</t>
   </si>
   <si>
-    <t>Roadmap v2.0 (phí gửi xe; điện, nước, internet) không thuộc backlog này hay Sprint 1-3: không có User Story, là Won't-have cho v1.0 và chỉ được liệt kê ở sheet Traceability (RAW-029, RAW-030) với Planned Sprint = Roadmap.</t>
+    <t>Roadmap v2.0 (phí gửi xe; điện, nước, internet) không thuộc backlog này hay Sprint 1-3: không có User Story, là Không sử dụng cho v1.0 và chỉ được liệt kê ở sheet Traceability (RAW-029, RAW-030) với Planned Sprint = Roadmap.</t>
   </si>
   <si>
     <t>Traceability Matrix — RAW to Acceptance Criteria</t>
@@ -1868,13 +1868,13 @@
     <t>— (không có User Story)</t>
   </si>
   <si>
-    <t>Won't</t>
+    <t>Không sử dụng</t>
   </si>
   <si>
     <t>Roadmap</t>
   </si>
   <si>
-    <t>ROADMAP. Won't-have cho v1.0. Không tạo Epic, Feature hay User Story. Số tiền phí gửi xe trong đề bài cần được xác nhận.</t>
+    <t>ROADMAP. Không sử dụng cho v1.0. Không tạo Epic, Feature hay User Story. Số tiền phí gửi xe trong đề bài cần được xác nhận.</t>
   </si>
   <si>
     <t>RAW-030</t>
@@ -1883,7 +1883,7 @@
     <t>[Roadmap v2.0] Quản lý các khoản thu hộ điện, nước, internet theo thông báo của nhà cung cấp dịch vụ.</t>
   </si>
   <si>
-    <t>ROADMAP. Won't-have cho v1.0. Không tạo Epic, Feature hay User Story.</t>
+    <t>ROADMAP. Không sử dụng cho v1.0. Không tạo Epic, Feature hay User Story.</t>
   </si>
   <si>
     <t>COVERAGE</t>
@@ -3878,7 +3878,7 @@
     <t>Quy tắc sắp xếp</t>
   </si>
   <si>
-    <t>1) Các story Must theo luồng chính (tài khoản, hộ gia đình, nhân khẩu, khoản thu, thu phí, tìm kiếm, thống kê); 2) một story luôn đứng sau các story mà nó phụ thuộc; 3) Should theo giá trị nghiệp vụ; 4) Could; 5) Won't hoặc Roadmap xếp cuối (backlog này không có).</t>
+    <t>1) Các story Must theo luồng chính (tài khoản, hộ gia đình, nhân khẩu, khoản thu, thu phí, tìm kiếm, thống kê); 2) một story luôn đứng sau các story mà nó phụ thuộc; 3) Should theo giá trị nghiệp vụ; 4) Could; 5) Không sử dụng hoặc Roadmap xếp cuối (backlog này không có).</t>
   </si>
   <si>
     <t>Thang điểm</t>
